--- a/outputs/marine_equipment/Контейнер_20ф_усиленный_27т.xlsx
+++ b/outputs/marine_equipment/Контейнер_20ф_усиленный_27т.xlsx
@@ -19209,7 +19209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -19527,64 +19527,109 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Ящиков встанет на клинкеты</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>на свободном полу мест нет, вся мелочь идет поверх задвижек</t>
+        </is>
+      </c>
+    </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Вес поверх клинкетов, кг</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>11668</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>ящики плюс фильтры и титан на них</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Нагрузка на клинкеты, кг/кв. м</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>1019</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>в двух двадцатифутовых выходит втрое меньше</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Чтобы не подавить арматуру</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>— На полу лежит 12 910 кг — это 931 кг на квадратный метр. Задвижки Ду200-350 кладем одним слоем  плашмя  фланцем вниз и никогда фланцем на фланец.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>— Ящиков с мелочью 19, по 600 кг. Они стоят на полу рядом с задвижками и в два уровня, а не поверх задвижек.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>— На ящики идет только верхний ярус — 2 214 кг фильтров и титана  это 117 кг на ящик при пределе 600.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>— Между рядами задвижек Ду250-350 шаг прокладок 300-400 мм, а не 600: длинный корпус на двух опорах прогибается и дает трещину по приливу.</t>
+          <t>— На полу лежит 12 910 кг — это 931 кг на квадратный метр. Задвижки Ду200-350 кладем одним слоем  плашмя  фланцем вниз и никогда фланцем на фланец.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>— Маховики снимаем, где снимаются, и кладем в ящик с биркой по номеру места. Нагрузку они не несут.</t>
+          <t>— Ящиков с мелочью 19, по 600 кг. Они стоят на полу рядом с задвижками и в два уровня, а не поверх задвижек.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>— Пустоты забиваем распорками из той же доски: в полном контейнере пустот мало, но продольные удары при маневрировании никуда не денутся.</t>
+          <t>— На ящики идет только верхний ярус — 2 214 кг фильтров и титана  это 117 кг на ящик при пределе 600.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>— Влагопоглотитель под крышу: месяц дороги дает конденсат.</t>
+          <t>— Между рядами задвижек Ду250-350 шаг прокладок 300-400 мм, а не 600: длинный корпус на двух опорах прогибается и дает трещину по приливу.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>— Маховики снимаем, где снимаются, и кладем в ящик с биркой по номеру места. Нагрузку они не несут.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>— Пустоты забиваем распорками из той же доски: в полном контейнере пустот мало, но продольные удары при маневрировании никуда не денутся.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>— Влагопоглотитель под крышу: месяц дороги дает конденсат.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>— Погрузчиком берем только поддоны и обрешетку. Голую задвижку вилами не поднимаем.</t>
         </is>

--- a/outputs/marine_equipment/Контейнер_20ф_усиленный_27т.xlsx
+++ b/outputs/marine_equipment/Контейнер_20ф_усиленный_27т.xlsx
@@ -19209,7 +19209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -19437,199 +19437,259 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Места под ящики</t>
+          <t>Клинкеты и места под ящики</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Клинкеты занимают пола, кв. м</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="n">
-        <v>11.5</v>
+          <t>Рядов клинкетов</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>26</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>83% пола, полоса 4.87 м</t>
+          <t>задвижка лежит на боку, шток горизонтально поперек</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Мест над клинкетами</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>16</v>
+          <t>Длина пола под клинкетами, м</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>10.7</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>два яруса ящиков</t>
+          <t>пол контейнера 5.898 м</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Мест на свободном полу</t>
+          <t>ЯРУСОВ КЛИНКЕТОВ</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>два яруса ящиков</t>
+          <t>больше одного — значит задвижка ляжет на задвижку</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>ВСЕГО мест</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="C15" s="2" t="inlineStr"/>
+          <t>Высота под клинкеты с досками, м</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>до потолка остается 1.39 м</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Нужно под мелочь</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>19</v>
+          <t>Свободного пола, м</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>ящиков по 600 кг</t>
+          <t>ряд ящиков просит 1.2 м</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Не хватает мест</t>
-        </is>
-      </c>
-      <c r="B17" s="26" t="n">
-        <v>3</v>
+          <t>Мест над клинкетами</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>8</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>если не ноль — столько ящиков в корпус не встает, это и есть нехватка объема</t>
+          <t>сколько ярусов ящиков встает сверху</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Ящиков встанет на клинкеты</t>
+          <t>Мест на свободном полу</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>на свободном полу мест нет, вся мелочь идет поверх задвижек</t>
+          <t>два яруса ящиков</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Вес поверх клинкетов, кг</t>
+          <t>ВСЕГО мест</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>11668</v>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>ящики плюс фильтры и титан на них</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
+          <t>Нужно под мелочь</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>ящиков по 600 кг</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Не хватает мест</t>
+        </is>
+      </c>
+      <c r="B21" s="26" t="n">
+        <v>11</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>если не ноль — столько ящиков в корпус не встает, это и есть нехватка объема</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Ящиков встанет на клинкеты</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>все, чему не хватило свободного пола</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Вес поверх клинкетов, кг</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>13441</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>ящики плюс фильтры и титан на них</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
           <t>Нагрузка на клинкеты, кг/кв. м</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n">
-        <v>1019</v>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>в двух двадцатифутовых выходит втрое меньше</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="B24" s="5" t="n">
+        <v>969</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>в двух двадцатифутовых выходит вдвое меньше, и там клинкеты лежат в один ярус</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Чтобы не подавить арматуру</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>— На полу лежит 12 910 кг — это 931 кг на квадратный метр. Задвижки Ду200-350 кладем одним слоем  плашмя  фланцем вниз и никогда фланцем на фланец.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>— Ящиков с мелочью 19, по 600 кг. Они стоят на полу рядом с задвижками и в два уровня, а не поверх задвижек.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>— На ящики идет только верхний ярус — 2 214 кг фильтров и титана  это 117 кг на ящик при пределе 600.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>— Между рядами задвижек Ду250-350 шаг прокладок 300-400 мм, а не 600: длинный корпус на двух опорах прогибается и дает трещину по приливу.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>— Маховики снимаем, где снимаются, и кладем в ящик с биркой по номеру места. Нагрузку они не несут.</t>
+          <t>— На полу лежит 12 910 кг — это 931 кг на квадратный метр. Задвижки Ду200-350 кладем одним слоем  плашмя  фланцем вниз и никогда фланцем на фланец.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>— Пустоты забиваем распорками из той же доски: в полном контейнере пустот мало, но продольные удары при маневрировании никуда не денутся.</t>
+          <t>— Ящиков с мелочью 19, по 600 кг. Они стоят на полу рядом с задвижками и в два уровня, а не поверх задвижек.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>— Влагопоглотитель под крышу: месяц дороги дает конденсат.</t>
+          <t>— На ящики идет только верхний ярус — 2 214 кг фильтров и титана  это 117 кг на ящик при пределе 600.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>— Между рядами задвижек Ду250-350 шаг прокладок 300-400 мм, а не 600: длинный корпус на двух опорах прогибается и дает трещину по приливу.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>— Маховики снимаем, где снимаются, и кладем в ящик с биркой по номеру места. Нагрузку они не несут.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>— Пустоты забиваем распорками из той же доски: в полном контейнере пустот мало, но продольные удары при маневрировании никуда не денутся.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>— Влагопоглотитель под крышу: месяц дороги дает конденсат.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>— Погрузчиком берем только поддоны и обрешетку. Голую задвижку вилами не поднимаем.</t>
         </is>

--- a/outputs/marine_equipment/Контейнер_20ф_усиленный_27т.xlsx
+++ b/outputs/marine_equipment/Контейнер_20ф_усиленный_27т.xlsx
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C5" s="2" t="inlineStr"/>
     </row>
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>2872</v>
+        <v>2879</v>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
     </row>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>26351</v>
+        <v>26320</v>
       </c>
       <c r="C7" s="2" t="inlineStr"/>
     </row>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>26996</v>
+        <v>26965</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>37.9</v>
+        <v>37.7</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -684,11 +684,11 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>948</v>
+        <v>975</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5 позиций — все без согласованной цены</t>
+          <t>2 позиции — все без согласованной цены</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
         <v>14.4</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>0.2895167175666953</v>
+        <v>0.2898532468351488</v>
       </c>
     </row>
     <row r="25">
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="C25" s="12" t="n">
-        <v>5281</v>
+        <v>5531</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>0.2004057189790377</v>
+        <v>0.2101522669681033</v>
       </c>
     </row>
     <row r="26">
@@ -873,13 +873,13 @@
         </is>
       </c>
       <c r="C26" s="12" t="n">
-        <v>11227</v>
+        <v>11293</v>
       </c>
       <c r="D26" s="13" t="n">
         <v>15.2</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>0.4260422670041342</v>
+        <v>0.4290468888800997</v>
       </c>
     </row>
     <row r="27">
@@ -894,13 +894,13 @@
         </is>
       </c>
       <c r="C27" s="12" t="n">
-        <v>2214</v>
+        <v>1867</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>0.08403529645008352</v>
+        <v>0.07094759731659897</v>
       </c>
     </row>
     <row r="29">
@@ -913,14 +913,14 @@
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>— Объем. По нашему справочнику габаритов груз занимает 37.9 куб. м плюс 0.92 на доску, а внутри контейнера 33. Справочник уже один раз завысил: массы задвижек были выше реальных почти вдвое. Если и объемы завышены, все войдет. Проверяем на первых ярусах и сразу считаем остаток.</t>
+          <t>— Объем. По нашему справочнику габаритов груз занимает 37.7 куб. м плюс 0.92 на доску, а внутри контейнера 33. Справочник уже один раз завысил: массы задвижек были выше реальных почти вдвое. Если и объемы завышены, все войдет. Проверяем на первых ярусах и сразу считаем остаток.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>— Вес. Паспортные 27 т — это брутто с доской. Доска съедает 646 кг, то есть 646 кг неувезенной арматуры. Характерные места взвешиваем: перегруз ловят на весах в порту.</t>
+          <t>— Вес. Паспортные 27 т — это брутто с доской. Доска съедает 645 кг, то есть 645 кг неувезенной арматуры. Характерные места взвешиваем: перегруз ловят на весах в порту.</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q310"/>
+  <dimension ref="A1:Q312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -13142,7 +13142,7 @@
     <row r="203">
       <c r="A203" s="16" t="inlineStr">
         <is>
-          <t>Клинкеты — 22 позиции, 201 шт, 9 662 кг</t>
+          <t>Клинкеты — 23 позиции, 202 шт, 9 728 кг</t>
         </is>
       </c>
       <c r="B203" s="16" t="n"/>
@@ -13901,10 +13901,10 @@
         <v>1</v>
       </c>
       <c r="H216" s="13" t="n">
-        <v>19.2</v>
+        <v>45</v>
       </c>
       <c r="I216" s="12" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="J216" s="18" t="n">
         <v>0.045</v>
@@ -13917,7 +13917,7 @@
       </c>
       <c r="M216" s="10" t="inlineStr">
         <is>
-          <t>Ярус 3, ящики</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="N216" s="11" t="inlineStr">
@@ -14425,10 +14425,14 @@
       </c>
       <c r="B225" s="11" t="inlineStr">
         <is>
-          <t>Электропривод к задвижке</t>
-        </is>
-      </c>
-      <c r="C225" s="20" t="inlineStr"/>
+          <t>Задвижки (желтая) ок. крышек</t>
+        </is>
+      </c>
+      <c r="C225" s="10" t="inlineStr">
+        <is>
+          <t>544-03.046</t>
+        </is>
+      </c>
       <c r="D225" s="10" t="n"/>
       <c r="E225" s="10" t="n"/>
       <c r="F225" s="10" t="inlineStr">
@@ -14466,93 +14470,89 @@
       </c>
       <c r="O225" s="10" t="inlineStr">
         <is>
+          <t>Склад 3</t>
+        </is>
+      </c>
+      <c r="P225" s="10" t="inlineStr"/>
+      <c r="Q225" s="10" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="10" t="n">
+        <v>215</v>
+      </c>
+      <c r="B226" s="11" t="inlineStr">
+        <is>
+          <t>Электропривод к задвижке</t>
+        </is>
+      </c>
+      <c r="C226" s="20" t="inlineStr"/>
+      <c r="D226" s="10" t="n"/>
+      <c r="E226" s="10" t="n"/>
+      <c r="F226" s="10" t="inlineStr">
+        <is>
+          <t>не указано</t>
+        </is>
+      </c>
+      <c r="G226" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H226" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="I226" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="J226" s="18" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K226" s="10" t="inlineStr"/>
+      <c r="L226" s="11" t="inlineStr">
+        <is>
+          <t>Б. Добор со склада</t>
+        </is>
+      </c>
+      <c r="M226" s="10" t="inlineStr">
+        <is>
+          <t>Ярус 3, ящики</t>
+        </is>
+      </c>
+      <c r="N226" s="11" t="inlineStr">
+        <is>
+          <t>Ящик сплошной, с перегородками</t>
+        </is>
+      </c>
+      <c r="O226" s="10" t="inlineStr">
+        <is>
           <t>Гараж 2</t>
         </is>
       </c>
-      <c r="P225" s="10" t="n">
+      <c r="P226" s="10" t="n">
         <v>50000</v>
       </c>
-      <c r="Q225" s="10" t="inlineStr"/>
-    </row>
-    <row r="226">
-      <c r="A226" s="16" t="inlineStr">
-        <is>
-          <t>Фильтры забортной воды — 10 позиций, 29 шт, 2 141 кг</t>
-        </is>
-      </c>
-      <c r="B226" s="16" t="n"/>
-      <c r="C226" s="16" t="n"/>
-      <c r="D226" s="16" t="n"/>
-      <c r="E226" s="16" t="n"/>
-      <c r="F226" s="16" t="n"/>
-      <c r="G226" s="16" t="n"/>
-      <c r="H226" s="16" t="n"/>
-      <c r="I226" s="16" t="n"/>
-      <c r="J226" s="16" t="n"/>
-      <c r="K226" s="16" t="n"/>
-      <c r="L226" s="16" t="n"/>
-      <c r="M226" s="16" t="n"/>
-      <c r="N226" s="16" t="n"/>
-      <c r="O226" s="16" t="n"/>
-      <c r="P226" s="16" t="n"/>
-      <c r="Q226" s="16" t="n"/>
+      <c r="Q226" s="10" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" s="10" t="n">
-        <v>215</v>
-      </c>
-      <c r="B227" s="11" t="inlineStr">
-        <is>
-          <t>Сетка на фильтр Ду20 маленькая</t>
-        </is>
-      </c>
-      <c r="C227" s="20" t="inlineStr"/>
-      <c r="D227" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="E227" s="10" t="n"/>
-      <c r="F227" s="10" t="inlineStr">
-        <is>
-          <t>не указано</t>
-        </is>
-      </c>
-      <c r="G227" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H227" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I227" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J227" s="18" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="K227" s="10" t="inlineStr"/>
-      <c r="L227" s="11" t="inlineStr">
-        <is>
-          <t>Б. Добор со склада</t>
-        </is>
-      </c>
-      <c r="M227" s="10" t="inlineStr">
-        <is>
-          <t>Ярус 4, верх</t>
-        </is>
-      </c>
-      <c r="N227" s="11" t="inlineStr">
-        <is>
-          <t>Обрешетка, ставится верхним ярусом на ящики</t>
-        </is>
-      </c>
-      <c r="O227" s="10" t="inlineStr">
-        <is>
-          <t>Склад 2</t>
-        </is>
-      </c>
-      <c r="P227" s="10" t="n">
-        <v>3000</v>
-      </c>
-      <c r="Q227" s="10" t="inlineStr"/>
+      <c r="A227" s="16" t="inlineStr">
+        <is>
+          <t>Фильтры забортной воды — 9 позиций, 28 шт, 1 828 кг</t>
+        </is>
+      </c>
+      <c r="B227" s="16" t="n"/>
+      <c r="C227" s="16" t="n"/>
+      <c r="D227" s="16" t="n"/>
+      <c r="E227" s="16" t="n"/>
+      <c r="F227" s="16" t="n"/>
+      <c r="G227" s="16" t="n"/>
+      <c r="H227" s="16" t="n"/>
+      <c r="I227" s="16" t="n"/>
+      <c r="J227" s="16" t="n"/>
+      <c r="K227" s="16" t="n"/>
+      <c r="L227" s="16" t="n"/>
+      <c r="M227" s="16" t="n"/>
+      <c r="N227" s="16" t="n"/>
+      <c r="O227" s="16" t="n"/>
+      <c r="P227" s="16" t="n"/>
+      <c r="Q227" s="16" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="10" t="n">
@@ -14560,12 +14560,12 @@
       </c>
       <c r="B228" s="11" t="inlineStr">
         <is>
-          <t>Фильтр забортной воды Ду 50</t>
+          <t>Сетка на фильтр Ду20 маленькая</t>
         </is>
       </c>
       <c r="C228" s="20" t="inlineStr"/>
       <c r="D228" s="10" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E228" s="10" t="n"/>
       <c r="F228" s="10" t="inlineStr">
@@ -14577,13 +14577,13 @@
         <v>1</v>
       </c>
       <c r="H228" s="13" t="n">
-        <v>7.8</v>
+        <v>1.5</v>
       </c>
       <c r="I228" s="12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J228" s="18" t="n">
-        <v>0.012</v>
+        <v>0.002</v>
       </c>
       <c r="K228" s="10" t="inlineStr"/>
       <c r="L228" s="11" t="inlineStr">
@@ -14593,21 +14593,21 @@
       </c>
       <c r="M228" s="10" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N228" s="11" t="inlineStr">
         <is>
-          <t>Обрешетка, ставится верхним ярусом на ящики</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="O228" s="10" t="inlineStr">
         <is>
-          <t>Фойе</t>
+          <t>Склад 2</t>
         </is>
       </c>
       <c r="P228" s="10" t="n">
-        <v>60000</v>
+        <v>3000</v>
       </c>
       <c r="Q228" s="10" t="inlineStr"/>
     </row>
@@ -14617,35 +14617,35 @@
       </c>
       <c r="B229" s="11" t="inlineStr">
         <is>
-          <t>Фильтр заборной воды ДУ 80</t>
+          <t>Фильтр забортной воды Ду 50</t>
         </is>
       </c>
       <c r="C229" s="20" t="inlineStr"/>
       <c r="D229" s="10" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="E229" s="10" t="n"/>
       <c r="F229" s="10" t="inlineStr">
         <is>
-          <t>б/у</t>
+          <t>не указано</t>
         </is>
       </c>
       <c r="G229" s="17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H229" s="13" t="n">
-        <v>22</v>
+        <v>7.8</v>
       </c>
       <c r="I229" s="12" t="n">
-        <v>110</v>
+        <v>8</v>
       </c>
       <c r="J229" s="18" t="n">
-        <v>0.15</v>
+        <v>0.012</v>
       </c>
       <c r="K229" s="10" t="inlineStr"/>
       <c r="L229" s="11" t="inlineStr">
         <is>
-          <t>А. Согласованный список</t>
+          <t>Б. Добор со склада</t>
         </is>
       </c>
       <c r="M229" s="10" t="inlineStr">
@@ -14660,10 +14660,12 @@
       </c>
       <c r="O229" s="10" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
-        </is>
-      </c>
-      <c r="P229" s="10" t="inlineStr"/>
+          <t>Фойе</t>
+        </is>
+      </c>
+      <c r="P229" s="10" t="n">
+        <v>60000</v>
+      </c>
       <c r="Q229" s="10" t="inlineStr"/>
     </row>
     <row r="230">
@@ -14672,35 +14674,35 @@
       </c>
       <c r="B230" s="11" t="inlineStr">
         <is>
-          <t>Сетка на фильтр Ду100 (медь) на кингстон РС-300</t>
+          <t>Фильтр заборной воды ДУ 80</t>
         </is>
       </c>
       <c r="C230" s="20" t="inlineStr"/>
       <c r="D230" s="10" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E230" s="10" t="n"/>
       <c r="F230" s="10" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>б/у</t>
         </is>
       </c>
       <c r="G230" s="17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H230" s="13" t="n">
-        <v>43.5</v>
+        <v>22</v>
       </c>
       <c r="I230" s="12" t="n">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="J230" s="18" t="n">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="K230" s="10" t="inlineStr"/>
       <c r="L230" s="11" t="inlineStr">
         <is>
-          <t>Б. Добор со склада</t>
+          <t>А. Согласованный список</t>
         </is>
       </c>
       <c r="M230" s="10" t="inlineStr">
@@ -14715,12 +14717,10 @@
       </c>
       <c r="O230" s="10" t="inlineStr">
         <is>
-          <t>Склад 2</t>
-        </is>
-      </c>
-      <c r="P230" s="10" t="n">
-        <v>10000</v>
-      </c>
+          <t>список менеджера, Прил. 2</t>
+        </is>
+      </c>
+      <c r="P230" s="10" t="inlineStr"/>
       <c r="Q230" s="10" t="inlineStr"/>
     </row>
     <row r="231">
@@ -14729,7 +14729,7 @@
       </c>
       <c r="B231" s="11" t="inlineStr">
         <is>
-          <t>Сетка на фильтр Ду100 или Ду80</t>
+          <t>Сетка на фильтр Ду100 (медь) на кингстон РС-300</t>
         </is>
       </c>
       <c r="C231" s="20" t="inlineStr"/>
@@ -14746,10 +14746,10 @@
         <v>2</v>
       </c>
       <c r="H231" s="13" t="n">
-        <v>43.5</v>
+        <v>8</v>
       </c>
       <c r="I231" s="12" t="n">
-        <v>87</v>
+        <v>16</v>
       </c>
       <c r="J231" s="18" t="n">
         <v>0.09</v>
@@ -14762,12 +14762,12 @@
       </c>
       <c r="M231" s="10" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="N231" s="11" t="inlineStr">
         <is>
-          <t>Обрешетка, ставится верхним ярусом на ящики</t>
+          <t>Поддон, прокладки между рядами</t>
         </is>
       </c>
       <c r="O231" s="10" t="inlineStr">
@@ -14786,7 +14786,7 @@
       </c>
       <c r="B232" s="11" t="inlineStr">
         <is>
-          <t>Фильтр забортной воды Ду 100</t>
+          <t>Сетка на фильтр Ду100 или Ду80</t>
         </is>
       </c>
       <c r="C232" s="20" t="inlineStr"/>
@@ -14796,52 +14796,46 @@
       <c r="E232" s="10" t="n"/>
       <c r="F232" s="10" t="inlineStr">
         <is>
-          <t>б/у</t>
+          <t>не указано</t>
         </is>
       </c>
       <c r="G232" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H232" s="13" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="I232" s="12" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="J232" s="18" t="n">
-        <v>0.045</v>
+        <v>0.09</v>
       </c>
       <c r="K232" s="10" t="inlineStr"/>
       <c r="L232" s="11" t="inlineStr">
         <is>
-          <t>А. Согласованный список</t>
+          <t>Б. Добор со склада</t>
         </is>
       </c>
       <c r="M232" s="10" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="N232" s="11" t="inlineStr">
         <is>
-          <t>Обрешетка, ставится верхним ярусом на ящики</t>
+          <t>Поддон, прокладки между рядами</t>
         </is>
       </c>
       <c r="O232" s="10" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
-        </is>
-      </c>
-      <c r="P232" s="10" t="inlineStr">
-        <is>
-          <t>55-650</t>
-        </is>
-      </c>
-      <c r="Q232" s="10" t="inlineStr">
-        <is>
-          <t>150-160</t>
-        </is>
-      </c>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="P232" s="10" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q232" s="10" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="10" t="n">
@@ -14849,39 +14843,35 @@
       </c>
       <c r="B233" s="11" t="inlineStr">
         <is>
-          <t>Фильтр фланц.прох. забортной воды Ду100 Ру4</t>
-        </is>
-      </c>
-      <c r="C233" s="10" t="inlineStr">
-        <is>
-          <t>427-03-109-2</t>
-        </is>
-      </c>
+          <t>Фильтр забортной воды Ду 100</t>
+        </is>
+      </c>
+      <c r="C233" s="20" t="inlineStr"/>
       <c r="D233" s="10" t="n">
         <v>100</v>
       </c>
       <c r="E233" s="10" t="n"/>
       <c r="F233" s="10" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>б/у</t>
         </is>
       </c>
       <c r="G233" s="17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H233" s="13" t="n">
-        <v>43.5</v>
+        <v>42</v>
       </c>
       <c r="I233" s="12" t="n">
-        <v>130</v>
+        <v>42</v>
       </c>
       <c r="J233" s="18" t="n">
-        <v>0.135</v>
+        <v>0.045</v>
       </c>
       <c r="K233" s="10" t="inlineStr"/>
       <c r="L233" s="11" t="inlineStr">
         <is>
-          <t>Б. Добор со склада</t>
+          <t>А. Согласованный список</t>
         </is>
       </c>
       <c r="M233" s="10" t="inlineStr">
@@ -14896,13 +14886,19 @@
       </c>
       <c r="O233" s="10" t="inlineStr">
         <is>
-          <t>Склад 2</t>
-        </is>
-      </c>
-      <c r="P233" s="10" t="n">
-        <v>120000</v>
-      </c>
-      <c r="Q233" s="10" t="inlineStr"/>
+          <t>список менеджера, Прил. 2</t>
+        </is>
+      </c>
+      <c r="P233" s="10" t="inlineStr">
+        <is>
+          <t>55-650</t>
+        </is>
+      </c>
+      <c r="Q233" s="10" t="inlineStr">
+        <is>
+          <t>150-160</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="10" t="n">
@@ -14910,35 +14906,39 @@
       </c>
       <c r="B234" s="11" t="inlineStr">
         <is>
-          <t>Фильтр заборной воды ДУ 150</t>
-        </is>
-      </c>
-      <c r="C234" s="20" t="inlineStr"/>
+          <t>Фильтр фланц.прох. забортной воды Ду100 Ру4</t>
+        </is>
+      </c>
+      <c r="C234" s="10" t="inlineStr">
+        <is>
+          <t>427-03-109-2</t>
+        </is>
+      </c>
       <c r="D234" s="10" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="E234" s="10" t="n"/>
       <c r="F234" s="10" t="inlineStr">
         <is>
-          <t>б/у</t>
+          <t>не указано</t>
         </is>
       </c>
       <c r="G234" s="17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H234" s="13" t="n">
-        <v>64</v>
+        <v>43.5</v>
       </c>
       <c r="I234" s="12" t="n">
-        <v>320</v>
+        <v>130</v>
       </c>
       <c r="J234" s="18" t="n">
-        <v>0.5</v>
+        <v>0.135</v>
       </c>
       <c r="K234" s="10" t="inlineStr"/>
       <c r="L234" s="11" t="inlineStr">
         <is>
-          <t>А. Согласованный список</t>
+          <t>Б. Добор со склада</t>
         </is>
       </c>
       <c r="M234" s="10" t="inlineStr">
@@ -14953,19 +14953,13 @@
       </c>
       <c r="O234" s="10" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
-        </is>
-      </c>
-      <c r="P234" s="10" t="inlineStr">
-        <is>
-          <t>75-90</t>
-        </is>
-      </c>
-      <c r="Q234" s="10" t="inlineStr">
-        <is>
-          <t>170-190</t>
-        </is>
-      </c>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="P234" s="10" t="n">
+        <v>120000</v>
+      </c>
+      <c r="Q234" s="10" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="10" t="n">
@@ -14973,12 +14967,12 @@
       </c>
       <c r="B235" s="11" t="inlineStr">
         <is>
-          <t>Фильтр забортной воды Ду200</t>
+          <t>Фильтр заборной воды ДУ 150</t>
         </is>
       </c>
       <c r="C235" s="20" t="inlineStr"/>
       <c r="D235" s="10" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="E235" s="10" t="n"/>
       <c r="F235" s="10" t="inlineStr">
@@ -14987,16 +14981,16 @@
         </is>
       </c>
       <c r="G235" s="17" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H235" s="13" t="n">
-        <v>148</v>
+        <v>64</v>
       </c>
       <c r="I235" s="12" t="n">
-        <v>1184</v>
+        <v>320</v>
       </c>
       <c r="J235" s="18" t="n">
-        <v>1.28</v>
+        <v>0.5</v>
       </c>
       <c r="K235" s="10" t="inlineStr"/>
       <c r="L235" s="11" t="inlineStr">
@@ -15021,12 +15015,12 @@
       </c>
       <c r="P235" s="10" t="inlineStr">
         <is>
-          <t>150-170</t>
+          <t>75-90</t>
         </is>
       </c>
       <c r="Q235" s="10" t="inlineStr">
         <is>
-          <t>280-320</t>
+          <t>170-190</t>
         </is>
       </c>
     </row>
@@ -15036,35 +15030,35 @@
       </c>
       <c r="B236" s="11" t="inlineStr">
         <is>
-          <t>Фильтр забортной воды Ду 300</t>
+          <t>Фильтр забортной воды Ду200</t>
         </is>
       </c>
       <c r="C236" s="20" t="inlineStr"/>
       <c r="D236" s="10" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E236" s="10" t="n"/>
       <c r="F236" s="10" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>б/у</t>
         </is>
       </c>
       <c r="G236" s="17" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H236" s="13" t="n">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="I236" s="12" t="n">
-        <v>172</v>
+        <v>1184</v>
       </c>
       <c r="J236" s="18" t="n">
-        <v>0.35</v>
+        <v>1.28</v>
       </c>
       <c r="K236" s="10" t="inlineStr"/>
       <c r="L236" s="11" t="inlineStr">
         <is>
-          <t>Б. Добор со склада</t>
+          <t>А. Согласованный список</t>
         </is>
       </c>
       <c r="M236" s="10" t="inlineStr">
@@ -15079,13 +15073,19 @@
       </c>
       <c r="O236" s="10" t="inlineStr">
         <is>
-          <t>Фойе</t>
-        </is>
-      </c>
-      <c r="P236" s="10" t="n">
-        <v>400000</v>
-      </c>
-      <c r="Q236" s="10" t="inlineStr"/>
+          <t>список менеджера, Прил. 2</t>
+        </is>
+      </c>
+      <c r="P236" s="10" t="inlineStr">
+        <is>
+          <t>150-170</t>
+        </is>
+      </c>
+      <c r="Q236" s="10" t="inlineStr">
+        <is>
+          <t>280-320</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="16" t="inlineStr">
@@ -16472,7 +16472,7 @@
     <row r="261">
       <c r="A261" s="16" t="inlineStr">
         <is>
-          <t>Коробки клапанные — 11 позиций, 62 шт, 3 317 кг</t>
+          <t>Коробки клапанные — 11 позиций, 65 шт, 3 490 кг</t>
         </is>
       </c>
       <c r="B261" s="16" t="n"/>
@@ -16811,16 +16811,16 @@
         </is>
       </c>
       <c r="G267" s="17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H267" s="13" t="n">
         <v>57.8</v>
       </c>
       <c r="I267" s="12" t="n">
-        <v>578</v>
+        <v>751</v>
       </c>
       <c r="J267" s="18" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="K267" s="10" t="inlineStr"/>
       <c r="L267" s="11" t="inlineStr">
@@ -18410,7 +18410,7 @@
     <row r="295">
       <c r="A295" s="16" t="inlineStr">
         <is>
-          <t>Электромагнитные клапаны — 3 позиции, 4 шт, 48 кг</t>
+          <t>Электромагнитные клапаны — 4 позиции, 7 шт, 85 кг</t>
         </is>
       </c>
       <c r="B295" s="16" t="n"/>
@@ -18620,98 +18620,80 @@
       <c r="Q298" s="10" t="inlineStr"/>
     </row>
     <row r="299">
-      <c r="A299" s="16" t="inlineStr">
+      <c r="A299" s="10" t="n">
+        <v>276</v>
+      </c>
+      <c r="B299" s="11" t="inlineStr">
+        <is>
+          <t>Клапан электромагнитный б/у</t>
+        </is>
+      </c>
+      <c r="C299" s="20" t="inlineStr"/>
+      <c r="D299" s="10" t="n"/>
+      <c r="E299" s="10" t="n"/>
+      <c r="F299" s="10" t="inlineStr">
+        <is>
+          <t>б/у</t>
+        </is>
+      </c>
+      <c r="G299" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H299" s="13" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="I299" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="J299" s="18" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K299" s="10" t="inlineStr"/>
+      <c r="L299" s="11" t="inlineStr">
+        <is>
+          <t>Б. Добор со склада</t>
+        </is>
+      </c>
+      <c r="M299" s="10" t="inlineStr">
+        <is>
+          <t>Ярус 3, ящики</t>
+        </is>
+      </c>
+      <c r="N299" s="11" t="inlineStr">
+        <is>
+          <t>Ящик сплошной, с перегородками</t>
+        </is>
+      </c>
+      <c r="O299" s="10" t="inlineStr">
+        <is>
+          <t>Склад 3</t>
+        </is>
+      </c>
+      <c r="P299" s="10" t="inlineStr"/>
+      <c r="Q299" s="10" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="16" t="inlineStr">
         <is>
           <t>Педальные клапаны — 2 позиции, 63 шт, 346 кг</t>
         </is>
       </c>
-      <c r="B299" s="16" t="n"/>
-      <c r="C299" s="16" t="n"/>
-      <c r="D299" s="16" t="n"/>
-      <c r="E299" s="16" t="n"/>
-      <c r="F299" s="16" t="n"/>
-      <c r="G299" s="16" t="n"/>
-      <c r="H299" s="16" t="n"/>
-      <c r="I299" s="16" t="n"/>
-      <c r="J299" s="16" t="n"/>
-      <c r="K299" s="16" t="n"/>
-      <c r="L299" s="16" t="n"/>
-      <c r="M299" s="16" t="n"/>
-      <c r="N299" s="16" t="n"/>
-      <c r="O299" s="16" t="n"/>
-      <c r="P299" s="16" t="n"/>
-      <c r="Q299" s="16" t="n"/>
-    </row>
-    <row r="300">
-      <c r="A300" s="10" t="n">
-        <v>276</v>
-      </c>
-      <c r="B300" s="11" t="inlineStr">
-        <is>
-          <t>Клапан педальный Ду25</t>
-        </is>
-      </c>
-      <c r="C300" s="10" t="inlineStr">
-        <is>
-          <t>М528-03.001</t>
-        </is>
-      </c>
-      <c r="D300" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="E300" s="10" t="n"/>
-      <c r="F300" s="10" t="inlineStr">
-        <is>
-          <t>б/у</t>
-        </is>
-      </c>
-      <c r="G300" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H300" s="13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="I300" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="J300" s="18" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="K300" s="19" t="inlineStr">
-        <is>
-          <t>педальный</t>
-        </is>
-      </c>
-      <c r="L300" s="11" t="inlineStr">
-        <is>
-          <t>А. Согласованный список</t>
-        </is>
-      </c>
-      <c r="M300" s="10" t="inlineStr">
-        <is>
-          <t>Ярус 3, ящики</t>
-        </is>
-      </c>
-      <c r="N300" s="11" t="inlineStr">
-        <is>
-          <t>Ящик сплошной, с перегородками</t>
-        </is>
-      </c>
-      <c r="O300" s="10" t="inlineStr">
-        <is>
-          <t>список менеджера, Прил. 2</t>
-        </is>
-      </c>
-      <c r="P300" s="10" t="inlineStr">
-        <is>
-          <t>15000</t>
-        </is>
-      </c>
-      <c r="Q300" s="10" t="inlineStr">
-        <is>
-          <t>30000</t>
-        </is>
-      </c>
+      <c r="B300" s="16" t="n"/>
+      <c r="C300" s="16" t="n"/>
+      <c r="D300" s="16" t="n"/>
+      <c r="E300" s="16" t="n"/>
+      <c r="F300" s="16" t="n"/>
+      <c r="G300" s="16" t="n"/>
+      <c r="H300" s="16" t="n"/>
+      <c r="I300" s="16" t="n"/>
+      <c r="J300" s="16" t="n"/>
+      <c r="K300" s="16" t="n"/>
+      <c r="L300" s="16" t="n"/>
+      <c r="M300" s="16" t="n"/>
+      <c r="N300" s="16" t="n"/>
+      <c r="O300" s="16" t="n"/>
+      <c r="P300" s="16" t="n"/>
+      <c r="Q300" s="16" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="10" t="n">
@@ -18719,7 +18701,7 @@
       </c>
       <c r="B301" s="11" t="inlineStr">
         <is>
-          <t>Клапан педальный Ду25 новый приход</t>
+          <t>Клапан педальный Ду25</t>
         </is>
       </c>
       <c r="C301" s="10" t="inlineStr">
@@ -18733,222 +18715,230 @@
       <c r="E301" s="10" t="n"/>
       <c r="F301" s="10" t="inlineStr">
         <is>
-          <t>новый</t>
+          <t>б/у</t>
         </is>
       </c>
       <c r="G301" s="17" t="n">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="H301" s="13" t="n">
         <v>5.5</v>
       </c>
       <c r="I301" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J301" s="18" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="K301" s="19" t="inlineStr">
+        <is>
+          <t>педальный</t>
+        </is>
+      </c>
+      <c r="L301" s="11" t="inlineStr">
+        <is>
+          <t>А. Согласованный список</t>
+        </is>
+      </c>
+      <c r="M301" s="10" t="inlineStr">
+        <is>
+          <t>Ярус 3, ящики</t>
+        </is>
+      </c>
+      <c r="N301" s="11" t="inlineStr">
+        <is>
+          <t>Ящик сплошной, с перегородками</t>
+        </is>
+      </c>
+      <c r="O301" s="10" t="inlineStr">
+        <is>
+          <t>список менеджера, Прил. 2</t>
+        </is>
+      </c>
+      <c r="P301" s="10" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="Q301" s="10" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="10" t="n">
+        <v>278</v>
+      </c>
+      <c r="B302" s="11" t="inlineStr">
+        <is>
+          <t>Клапан педальный Ду25 новый приход</t>
+        </is>
+      </c>
+      <c r="C302" s="10" t="inlineStr">
+        <is>
+          <t>М528-03.001</t>
+        </is>
+      </c>
+      <c r="D302" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="E302" s="10" t="n"/>
+      <c r="F302" s="10" t="inlineStr">
+        <is>
+          <t>новый</t>
+        </is>
+      </c>
+      <c r="G302" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="H302" s="13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I302" s="12" t="n">
         <v>341</v>
       </c>
-      <c r="J301" s="18" t="n">
+      <c r="J302" s="18" t="n">
         <v>0.186</v>
       </c>
-      <c r="K301" s="19" t="inlineStr">
+      <c r="K302" s="19" t="inlineStr">
         <is>
           <t>педальный</t>
         </is>
       </c>
-      <c r="L301" s="11" t="inlineStr">
+      <c r="L302" s="11" t="inlineStr">
         <is>
           <t>А. Согласованный список</t>
         </is>
       </c>
-      <c r="M301" s="10" t="inlineStr">
-        <is>
-          <t>Ярус 3, ящики</t>
-        </is>
-      </c>
-      <c r="N301" s="11" t="inlineStr">
+      <c r="M302" s="10" t="inlineStr">
+        <is>
+          <t>Ярус 3, ящики</t>
+        </is>
+      </c>
+      <c r="N302" s="11" t="inlineStr">
         <is>
           <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
-      <c r="O301" s="10" t="inlineStr">
+      <c r="O302" s="10" t="inlineStr">
         <is>
           <t>список менеджера, Прил. 2</t>
         </is>
       </c>
-      <c r="P301" s="10" t="inlineStr">
+      <c r="P302" s="10" t="inlineStr">
         <is>
           <t>15000</t>
         </is>
       </c>
-      <c r="Q301" s="10" t="inlineStr">
+      <c r="Q302" s="10" t="inlineStr">
         <is>
           <t>30000</t>
         </is>
       </c>
     </row>
-    <row r="302">
-      <c r="A302" s="16" t="inlineStr">
+    <row r="303">
+      <c r="A303" s="16" t="inlineStr">
         <is>
           <t>Эжекторы — 1 позиция, 1 шт, 4 кг</t>
         </is>
       </c>
-      <c r="B302" s="16" t="n"/>
-      <c r="C302" s="16" t="n"/>
-      <c r="D302" s="16" t="n"/>
-      <c r="E302" s="16" t="n"/>
-      <c r="F302" s="16" t="n"/>
-      <c r="G302" s="16" t="n"/>
-      <c r="H302" s="16" t="n"/>
-      <c r="I302" s="16" t="n"/>
-      <c r="J302" s="16" t="n"/>
-      <c r="K302" s="16" t="n"/>
-      <c r="L302" s="16" t="n"/>
-      <c r="M302" s="16" t="n"/>
-      <c r="N302" s="16" t="n"/>
-      <c r="O302" s="16" t="n"/>
-      <c r="P302" s="16" t="n"/>
-      <c r="Q302" s="16" t="n"/>
-    </row>
-    <row r="303">
-      <c r="A303" s="10" t="n">
-        <v>278</v>
-      </c>
-      <c r="B303" s="11" t="inlineStr">
+      <c r="B303" s="16" t="n"/>
+      <c r="C303" s="16" t="n"/>
+      <c r="D303" s="16" t="n"/>
+      <c r="E303" s="16" t="n"/>
+      <c r="F303" s="16" t="n"/>
+      <c r="G303" s="16" t="n"/>
+      <c r="H303" s="16" t="n"/>
+      <c r="I303" s="16" t="n"/>
+      <c r="J303" s="16" t="n"/>
+      <c r="K303" s="16" t="n"/>
+      <c r="L303" s="16" t="n"/>
+      <c r="M303" s="16" t="n"/>
+      <c r="N303" s="16" t="n"/>
+      <c r="O303" s="16" t="n"/>
+      <c r="P303" s="16" t="n"/>
+      <c r="Q303" s="16" t="n"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="10" t="n">
+        <v>279</v>
+      </c>
+      <c r="B304" s="11" t="inlineStr">
         <is>
           <t>Эжектор ВЭЖ 6,3</t>
         </is>
       </c>
-      <c r="C303" s="20" t="inlineStr"/>
-      <c r="D303" s="10" t="n"/>
-      <c r="E303" s="10" t="n"/>
-      <c r="F303" s="10" t="inlineStr">
+      <c r="C304" s="20" t="inlineStr"/>
+      <c r="D304" s="10" t="n"/>
+      <c r="E304" s="10" t="n"/>
+      <c r="F304" s="10" t="inlineStr">
         <is>
           <t>б/у</t>
         </is>
       </c>
-      <c r="G303" s="17" t="n">
+      <c r="G304" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="H303" s="13" t="n">
+      <c r="H304" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="I303" s="12" t="n">
+      <c r="I304" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="J303" s="18" t="n">
+      <c r="J304" s="18" t="n">
         <v>0.01</v>
       </c>
-      <c r="K303" s="10" t="inlineStr"/>
-      <c r="L303" s="11" t="inlineStr">
+      <c r="K304" s="10" t="inlineStr"/>
+      <c r="L304" s="11" t="inlineStr">
         <is>
           <t>А. Согласованный список</t>
         </is>
       </c>
-      <c r="M303" s="10" t="inlineStr">
-        <is>
-          <t>Ярус 3, ящики</t>
-        </is>
-      </c>
-      <c r="N303" s="11" t="inlineStr">
+      <c r="M304" s="10" t="inlineStr">
+        <is>
+          <t>Ярус 3, ящики</t>
+        </is>
+      </c>
+      <c r="N304" s="11" t="inlineStr">
         <is>
           <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
-      <c r="O303" s="10" t="inlineStr">
+      <c r="O304" s="10" t="inlineStr">
         <is>
           <t>список менеджера, Прил. 3</t>
         </is>
       </c>
-      <c r="P303" s="10" t="inlineStr">
+      <c r="P304" s="10" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="Q303" s="10" t="inlineStr"/>
-    </row>
-    <row r="304">
-      <c r="A304" s="16" t="inlineStr">
-        <is>
-          <t>Без описания — уточнить — 5 позиций, 7 шт, 163 кг</t>
-        </is>
-      </c>
-      <c r="B304" s="16" t="n"/>
-      <c r="C304" s="16" t="n"/>
-      <c r="D304" s="16" t="n"/>
-      <c r="E304" s="16" t="n"/>
-      <c r="F304" s="16" t="n"/>
-      <c r="G304" s="16" t="n"/>
-      <c r="H304" s="16" t="n"/>
-      <c r="I304" s="16" t="n"/>
-      <c r="J304" s="16" t="n"/>
-      <c r="K304" s="16" t="n"/>
-      <c r="L304" s="16" t="n"/>
-      <c r="M304" s="16" t="n"/>
-      <c r="N304" s="16" t="n"/>
-      <c r="O304" s="16" t="n"/>
-      <c r="P304" s="16" t="n"/>
-      <c r="Q304" s="16" t="n"/>
+      <c r="Q304" s="10" t="inlineStr"/>
     </row>
     <row r="305">
-      <c r="A305" s="10" t="n">
-        <v>279</v>
-      </c>
-      <c r="B305" s="11" t="inlineStr">
-        <is>
-          <t>Клапан Ду20/10</t>
-        </is>
-      </c>
-      <c r="C305" s="10" t="inlineStr">
-        <is>
-          <t>581-С6.73</t>
-        </is>
-      </c>
-      <c r="D305" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="E305" s="10" t="n"/>
-      <c r="F305" s="10" t="inlineStr">
-        <is>
-          <t>новая</t>
-        </is>
-      </c>
-      <c r="G305" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="H305" s="13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="I305" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J305" s="18" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="K305" s="10" t="inlineStr"/>
-      <c r="L305" s="11" t="inlineStr">
-        <is>
-          <t>А. Согласованный список</t>
-        </is>
-      </c>
-      <c r="M305" s="10" t="inlineStr">
-        <is>
-          <t>Ярус 3, ящики</t>
-        </is>
-      </c>
-      <c r="N305" s="11" t="inlineStr">
-        <is>
-          <t>Ящик сплошной, с перегородками</t>
-        </is>
-      </c>
-      <c r="O305" s="10" t="inlineStr">
-        <is>
-          <t>список менеджера, Прил. 3</t>
-        </is>
-      </c>
-      <c r="P305" s="10" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q305" s="10" t="inlineStr"/>
+      <c r="A305" s="16" t="inlineStr">
+        <is>
+          <t>Без описания — уточнить — 6 позиций, 8 шт, 170 кг</t>
+        </is>
+      </c>
+      <c r="B305" s="16" t="n"/>
+      <c r="C305" s="16" t="n"/>
+      <c r="D305" s="16" t="n"/>
+      <c r="E305" s="16" t="n"/>
+      <c r="F305" s="16" t="n"/>
+      <c r="G305" s="16" t="n"/>
+      <c r="H305" s="16" t="n"/>
+      <c r="I305" s="16" t="n"/>
+      <c r="J305" s="16" t="n"/>
+      <c r="K305" s="16" t="n"/>
+      <c r="L305" s="16" t="n"/>
+      <c r="M305" s="16" t="n"/>
+      <c r="N305" s="16" t="n"/>
+      <c r="O305" s="16" t="n"/>
+      <c r="P305" s="16" t="n"/>
+      <c r="Q305" s="16" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="10" t="n">
@@ -18956,54 +18946,60 @@
       </c>
       <c r="B306" s="11" t="inlineStr">
         <is>
-          <t>Клапан проходной ДУ 125 корпус</t>
-        </is>
-      </c>
-      <c r="C306" s="20" t="inlineStr"/>
+          <t>Клапан Ду20/10</t>
+        </is>
+      </c>
+      <c r="C306" s="10" t="inlineStr">
+        <is>
+          <t>581-С6.73</t>
+        </is>
+      </c>
       <c r="D306" s="10" t="n">
-        <v>125</v>
+        <v>20</v>
       </c>
       <c r="E306" s="10" t="n"/>
       <c r="F306" s="10" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>новая</t>
         </is>
       </c>
       <c r="G306" s="17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H306" s="13" t="n">
-        <v>135.3</v>
+        <v>2.4</v>
       </c>
       <c r="I306" s="12" t="n">
-        <v>135</v>
+        <v>7</v>
       </c>
       <c r="J306" s="18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.006</v>
       </c>
       <c r="K306" s="10" t="inlineStr"/>
       <c r="L306" s="11" t="inlineStr">
         <is>
-          <t>Б. Добор со склада</t>
+          <t>А. Согласованный список</t>
         </is>
       </c>
       <c r="M306" s="10" t="inlineStr">
         <is>
-          <t>Ярус 2, рядом на полу</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="N306" s="11" t="inlineStr">
         <is>
-          <t>Поддон, прокладки между рядами</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="O306" s="10" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
-        </is>
-      </c>
-      <c r="P306" s="10" t="n">
-        <v>37000</v>
+          <t>список менеджера, Прил. 3</t>
+        </is>
+      </c>
+      <c r="P306" s="10" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
       </c>
       <c r="Q306" s="10" t="inlineStr"/>
     </row>
@@ -19013,60 +19009,54 @@
       </c>
       <c r="B307" s="11" t="inlineStr">
         <is>
-          <t>Кланан Рр18-2 45/25</t>
-        </is>
-      </c>
-      <c r="C307" s="10" t="inlineStr">
-        <is>
-          <t>2619802505</t>
-        </is>
-      </c>
-      <c r="D307" s="10" t="n"/>
-      <c r="E307" s="10" t="n">
-        <v>18</v>
-      </c>
+          <t>Клапан проходной ДУ 125 корпус</t>
+        </is>
+      </c>
+      <c r="C307" s="20" t="inlineStr"/>
+      <c r="D307" s="10" t="n">
+        <v>125</v>
+      </c>
+      <c r="E307" s="10" t="n"/>
       <c r="F307" s="10" t="inlineStr">
         <is>
-          <t>новая</t>
+          <t>не указано</t>
         </is>
       </c>
       <c r="G307" s="17" t="n">
         <v>1</v>
       </c>
       <c r="H307" s="13" t="n">
-        <v>6.8</v>
+        <v>135.3</v>
       </c>
       <c r="I307" s="12" t="n">
-        <v>7</v>
+        <v>135</v>
       </c>
       <c r="J307" s="18" t="n">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K307" s="10" t="inlineStr"/>
       <c r="L307" s="11" t="inlineStr">
         <is>
-          <t>А. Согласованный список</t>
+          <t>Б. Добор со склада</t>
         </is>
       </c>
       <c r="M307" s="10" t="inlineStr">
         <is>
-          <t>Ярус 3, ящики</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="N307" s="11" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Поддон, прокладки между рядами</t>
         </is>
       </c>
       <c r="O307" s="10" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
-        </is>
-      </c>
-      <c r="P307" s="10" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
+          <t>Склад 1А/1Б</t>
+        </is>
+      </c>
+      <c r="P307" s="10" t="n">
+        <v>37000</v>
       </c>
       <c r="Q307" s="10" t="inlineStr"/>
     </row>
@@ -19076,19 +19066,21 @@
       </c>
       <c r="B308" s="11" t="inlineStr">
         <is>
-          <t>Клапан</t>
+          <t>Кланан Рр18-2 45/25</t>
         </is>
       </c>
       <c r="C308" s="10" t="inlineStr">
         <is>
-          <t>587-182.126</t>
+          <t>2619802505</t>
         </is>
       </c>
       <c r="D308" s="10" t="n"/>
-      <c r="E308" s="10" t="n"/>
+      <c r="E308" s="10" t="n">
+        <v>18</v>
+      </c>
       <c r="F308" s="10" t="inlineStr">
         <is>
-          <t>не указано</t>
+          <t>новая</t>
         </is>
       </c>
       <c r="G308" s="17" t="n">
@@ -19106,7 +19098,7 @@
       <c r="K308" s="10" t="inlineStr"/>
       <c r="L308" s="11" t="inlineStr">
         <is>
-          <t>Б. Добор со склада</t>
+          <t>А. Согласованный список</t>
         </is>
       </c>
       <c r="M308" s="10" t="inlineStr">
@@ -19121,10 +19113,14 @@
       </c>
       <c r="O308" s="10" t="inlineStr">
         <is>
-          <t>Склад 2</t>
-        </is>
-      </c>
-      <c r="P308" s="10" t="inlineStr"/>
+          <t>список менеджера, Прил. 3</t>
+        </is>
+      </c>
+      <c r="P308" s="10" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="Q308" s="10" t="inlineStr"/>
     </row>
     <row r="309">
@@ -19133,10 +19129,14 @@
       </c>
       <c r="B309" s="11" t="inlineStr">
         <is>
-          <t>Судовая запорная арматура</t>
-        </is>
-      </c>
-      <c r="C309" s="20" t="inlineStr"/>
+          <t>Кланан Рр18-2 45/25</t>
+        </is>
+      </c>
+      <c r="C309" s="10" t="inlineStr">
+        <is>
+          <t>2619802505</t>
+        </is>
+      </c>
       <c r="D309" s="10" t="n"/>
       <c r="E309" s="10" t="n"/>
       <c r="F309" s="10" t="inlineStr">
@@ -19174,28 +19174,138 @@
       </c>
       <c r="O309" s="10" t="inlineStr">
         <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="P309" s="10" t="inlineStr"/>
+      <c r="Q309" s="10" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="10" t="n">
+        <v>284</v>
+      </c>
+      <c r="B310" s="11" t="inlineStr">
+        <is>
+          <t>Клапан</t>
+        </is>
+      </c>
+      <c r="C310" s="10" t="inlineStr">
+        <is>
+          <t>587-182.126</t>
+        </is>
+      </c>
+      <c r="D310" s="10" t="n"/>
+      <c r="E310" s="10" t="n"/>
+      <c r="F310" s="10" t="inlineStr">
+        <is>
+          <t>не указано</t>
+        </is>
+      </c>
+      <c r="G310" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H310" s="13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I310" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J310" s="18" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K310" s="10" t="inlineStr"/>
+      <c r="L310" s="11" t="inlineStr">
+        <is>
+          <t>Б. Добор со склада</t>
+        </is>
+      </c>
+      <c r="M310" s="10" t="inlineStr">
+        <is>
+          <t>Ярус 3, ящики</t>
+        </is>
+      </c>
+      <c r="N310" s="11" t="inlineStr">
+        <is>
+          <t>Ящик сплошной, с перегородками</t>
+        </is>
+      </c>
+      <c r="O310" s="10" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="P310" s="10" t="inlineStr"/>
+      <c r="Q310" s="10" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="10" t="n">
+        <v>285</v>
+      </c>
+      <c r="B311" s="11" t="inlineStr">
+        <is>
+          <t>Судовая запорная арматура</t>
+        </is>
+      </c>
+      <c r="C311" s="20" t="inlineStr"/>
+      <c r="D311" s="10" t="n"/>
+      <c r="E311" s="10" t="n"/>
+      <c r="F311" s="10" t="inlineStr">
+        <is>
+          <t>не указано</t>
+        </is>
+      </c>
+      <c r="G311" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H311" s="13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I311" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J311" s="18" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K311" s="10" t="inlineStr"/>
+      <c r="L311" s="11" t="inlineStr">
+        <is>
+          <t>Б. Добор со склада</t>
+        </is>
+      </c>
+      <c r="M311" s="10" t="inlineStr">
+        <is>
+          <t>Ярус 3, ящики</t>
+        </is>
+      </c>
+      <c r="N311" s="11" t="inlineStr">
+        <is>
+          <t>Ящик сплошной, с перегородками</t>
+        </is>
+      </c>
+      <c r="O311" s="10" t="inlineStr">
+        <is>
           <t>Менеджерская</t>
         </is>
       </c>
-      <c r="P309" s="10" t="n">
+      <c r="P311" s="10" t="n">
         <v>10000</v>
       </c>
-      <c r="Q309" s="10" t="inlineStr"/>
-    </row>
-    <row r="310">
-      <c r="B310" s="21" t="inlineStr">
+      <c r="Q311" s="10" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="B312" s="21" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="G310" s="5" t="n">
-        <v>2872</v>
-      </c>
-      <c r="I310" s="5" t="n">
-        <v>26350.8099432709</v>
-      </c>
-      <c r="J310" s="8" t="n">
-        <v>37.92650000000003</v>
+      <c r="G312" s="5" t="n">
+        <v>2879</v>
+      </c>
+      <c r="I312" s="5" t="n">
+        <v>26320.21577573891</v>
+      </c>
+      <c r="J312" s="8" t="n">
+        <v>37.71650000000002</v>
       </c>
     </row>
   </sheetData>
@@ -19295,7 +19405,7 @@
         </is>
       </c>
       <c r="D5" s="24" t="n">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="E5" s="22" t="n">
         <v>0.92</v>
@@ -19332,10 +19442,10 @@
         <v>1.04</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>8275</v>
+        <v>8274</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>18725</v>
+        <v>18726</v>
       </c>
     </row>
     <row r="7">
@@ -19355,19 +19465,19 @@
         </is>
       </c>
       <c r="D7" s="12" t="n">
-        <v>5281</v>
+        <v>5531</v>
       </c>
       <c r="E7" s="25" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="F7" s="25" t="n">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>13555</v>
+        <v>13805</v>
       </c>
       <c r="H7" s="12" t="n">
-        <v>13445</v>
+        <v>13195</v>
       </c>
     </row>
     <row r="8">
@@ -19387,7 +19497,7 @@
         </is>
       </c>
       <c r="D8" s="12" t="n">
-        <v>11227</v>
+        <v>11293</v>
       </c>
       <c r="E8" s="25" t="n">
         <v>15.2</v>
@@ -19396,10 +19506,10 @@
         <v>1.09</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>24782</v>
+        <v>25098</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>2218</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="9">
@@ -19419,19 +19529,19 @@
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>2214</v>
+        <v>1867</v>
       </c>
       <c r="E9" s="25" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="F9" s="25" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>26996</v>
+        <v>26965</v>
       </c>
       <c r="H9" s="12" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
@@ -19609,7 +19719,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>13441</v>
+        <v>13160</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
@@ -19624,7 +19734,7 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>969</v>
+        <v>949</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
@@ -19642,7 +19752,7 @@
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>— На полу лежит 12 910 кг — это 931 кг на квадратный метр. Задвижки Ду200-350 кладем одним слоем  плашмя  фланцем вниз и никогда фланцем на фланец.</t>
+          <t>— На полу лежит 13 160 кг — это 949 кг на квадратный метр. Задвижки Ду200-350 кладем одним слоем  плашмя  фланцем вниз и никогда фланцем на фланец.</t>
         </is>
       </c>
     </row>
@@ -19656,7 +19766,7 @@
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>— На ящики идет только верхний ярус — 2 214 кг фильтров и титана  это 117 кг на ящик при пределе 600.</t>
+          <t>— На ящики идет только верхний ярус — 1 867 кг фильтров и титана  это 98 кг на ящик при пределе 600.</t>
         </is>
       </c>
     </row>
@@ -19706,7 +19816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -19832,7 +19942,7 @@
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>Клинкеты — 2 позиции, 24 шт, 731 кг</t>
+          <t>Клинкеты — 2 позиции, 23 шт, 975 кг</t>
         </is>
       </c>
       <c r="B5" s="16" t="n"/>
@@ -19875,10 +19985,10 @@
         <v>11</v>
       </c>
       <c r="H6" s="13" t="n">
-        <v>19.2</v>
+        <v>45</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>211</v>
+        <v>495</v>
       </c>
       <c r="J6" s="18" t="n">
         <v>0.495</v>
@@ -19891,7 +20001,7 @@
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
-          <t>Ярус 3, ящики</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="N6" s="11" t="inlineStr">
@@ -19929,16 +20039,16 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H7" s="13" t="n">
         <v>40</v>
       </c>
       <c r="I7" s="12" t="n">
-        <v>520</v>
+        <v>480</v>
       </c>
       <c r="J7" s="18" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="K7" s="10" t="inlineStr"/>
       <c r="L7" s="11" t="inlineStr">
@@ -19965,253 +20075,19 @@
       <c r="Q7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>Коробки клапанные — 1 позиция, 3 шт, 173 кг</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="16" t="n"/>
-      <c r="D8" s="16" t="n"/>
-      <c r="E8" s="16" t="n"/>
-      <c r="F8" s="16" t="n"/>
-      <c r="G8" s="16" t="n"/>
-      <c r="H8" s="16" t="n"/>
-      <c r="I8" s="16" t="n"/>
-      <c r="J8" s="16" t="n"/>
-      <c r="K8" s="16" t="n"/>
-      <c r="L8" s="16" t="n"/>
-      <c r="M8" s="16" t="n"/>
-      <c r="N8" s="16" t="n"/>
-      <c r="O8" s="16" t="n"/>
-      <c r="P8" s="16" t="n"/>
-      <c r="Q8" s="16" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>Коробка 2-х клапановая фланцевая Ду80</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr"/>
-      <c r="D9" s="10" t="n">
-        <v>80</v>
-      </c>
-      <c r="E9" s="10" t="n"/>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>новый</t>
-        </is>
-      </c>
-      <c r="G9" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="H9" s="13" t="n">
-        <v>57.8</v>
-      </c>
-      <c r="I9" s="12" t="n">
-        <v>173</v>
-      </c>
-      <c r="J9" s="18" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="K9" s="10" t="inlineStr"/>
-      <c r="L9" s="11" t="inlineStr">
-        <is>
-          <t>Б. Добор со склада</t>
-        </is>
-      </c>
-      <c r="M9" s="10" t="inlineStr">
-        <is>
-          <t>Ярус 2, рядом на полу</t>
-        </is>
-      </c>
-      <c r="N9" s="11" t="inlineStr">
-        <is>
-          <t>Обрешетка на поддоне</t>
-        </is>
-      </c>
-      <c r="O9" s="10" t="inlineStr">
-        <is>
-          <t>Склад 2</t>
-        </is>
-      </c>
-      <c r="P9" s="10" t="inlineStr"/>
-      <c r="Q9" s="10" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>Электромагнитные клапаны — 1 позиция, 3 шт, 37 кг</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
-      <c r="G10" s="16" t="n"/>
-      <c r="H10" s="16" t="n"/>
-      <c r="I10" s="16" t="n"/>
-      <c r="J10" s="16" t="n"/>
-      <c r="K10" s="16" t="n"/>
-      <c r="L10" s="16" t="n"/>
-      <c r="M10" s="16" t="n"/>
-      <c r="N10" s="16" t="n"/>
-      <c r="O10" s="16" t="n"/>
-      <c r="P10" s="16" t="n"/>
-      <c r="Q10" s="16" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Клапан электромагнитный б/у</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr"/>
-      <c r="D11" s="10" t="n"/>
-      <c r="E11" s="10" t="n"/>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t>б/у</t>
-        </is>
-      </c>
-      <c r="G11" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="H11" s="13" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="I11" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="J11" s="18" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K11" s="10" t="inlineStr"/>
-      <c r="L11" s="11" t="inlineStr">
-        <is>
-          <t>Б. Добор со склада</t>
-        </is>
-      </c>
-      <c r="M11" s="10" t="inlineStr">
-        <is>
-          <t>Ярус 3, ящики</t>
-        </is>
-      </c>
-      <c r="N11" s="11" t="inlineStr">
-        <is>
-          <t>Ящик сплошной, с перегородками</t>
-        </is>
-      </c>
-      <c r="O11" s="10" t="inlineStr">
-        <is>
-          <t>Склад 3</t>
-        </is>
-      </c>
-      <c r="P11" s="10" t="inlineStr"/>
-      <c r="Q11" s="10" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>Без описания — уточнить — 1 позиция, 1 шт, 7 кг</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="16" t="n"/>
-      <c r="D12" s="16" t="n"/>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="16" t="n"/>
-      <c r="G12" s="16" t="n"/>
-      <c r="H12" s="16" t="n"/>
-      <c r="I12" s="16" t="n"/>
-      <c r="J12" s="16" t="n"/>
-      <c r="K12" s="16" t="n"/>
-      <c r="L12" s="16" t="n"/>
-      <c r="M12" s="16" t="n"/>
-      <c r="N12" s="16" t="n"/>
-      <c r="O12" s="16" t="n"/>
-      <c r="P12" s="16" t="n"/>
-      <c r="Q12" s="16" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>Кланан Рр18-2 45/25</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>2619802505</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>не указано</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="I13" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J13" s="18" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="K13" s="10" t="inlineStr"/>
-      <c r="L13" s="11" t="inlineStr">
-        <is>
-          <t>Б. Добор со склада</t>
-        </is>
-      </c>
-      <c r="M13" s="10" t="inlineStr">
-        <is>
-          <t>Ярус 3, ящики</t>
-        </is>
-      </c>
-      <c r="N13" s="11" t="inlineStr">
-        <is>
-          <t>Ящик сплошной, с перегородками</t>
-        </is>
-      </c>
-      <c r="O13" s="10" t="inlineStr">
-        <is>
-          <t>Склад 2</t>
-        </is>
-      </c>
-      <c r="P13" s="10" t="inlineStr"/>
-      <c r="Q13" s="10" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="G14" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v>947.7732363176621</v>
-      </c>
-      <c r="J14" s="8" t="n">
-        <v>0.755</v>
+      <c r="G8" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>975</v>
+      </c>
+      <c r="J8" s="8" t="n">
+        <v>0.615</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/marine_equipment/Контейнер_20ф_усиленный_27т.xlsx
+++ b/outputs/marine_equipment/Контейнер_20ф_усиленный_27т.xlsx
@@ -14452,7 +14452,11 @@
       <c r="J225" s="18" t="n">
         <v>0.01</v>
       </c>
-      <c r="K225" s="10" t="inlineStr"/>
+      <c r="K225" s="19" t="inlineStr">
+        <is>
+          <t>сталь</t>
+        </is>
+      </c>
       <c r="L225" s="11" t="inlineStr">
         <is>
           <t>Б. Добор со склада</t>
@@ -20050,7 +20054,11 @@
       <c r="J7" s="18" t="n">
         <v>0.12</v>
       </c>
-      <c r="K7" s="10" t="inlineStr"/>
+      <c r="K7" s="19" t="inlineStr">
+        <is>
+          <t>сталь</t>
+        </is>
+      </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
           <t>Б. Добор со склада</t>
